--- a/Data/Base Day TUE.xlsx
+++ b/Data/Base Day TUE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\UNI\MSc DTU\Masterarbeit\RollingStock\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFA7948-EDB5-4FAD-B66A-56F10225860C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44887652-818A-4CC8-8322-F4BCDDDAB171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="326">
   <si>
     <t>Settings</t>
   </si>
@@ -1021,6 +1021,9 @@
   </si>
   <si>
     <t>Limitation on the number of units of equipment at the station at the end of the period</t>
+  </si>
+  <si>
+    <t>Electrified</t>
   </si>
 </sst>
 </file>
@@ -3546,7 +3549,7 @@
   <sheetPr codeName="Ark8">
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -3557,7 +3560,7 @@
     <col min="8" max="8" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -3582,8 +3585,11 @@
       <c r="H1" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>203</v>
       </c>
@@ -3608,8 +3614,11 @@
       <c r="H2">
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>205</v>
       </c>
@@ -3634,8 +3643,11 @@
       <c r="H3">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -3660,8 +3672,11 @@
       <c r="H4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>208</v>
       </c>
@@ -3686,8 +3701,11 @@
       <c r="H5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>210</v>
       </c>
@@ -3712,8 +3730,11 @@
       <c r="H6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>212</v>
       </c>
@@ -3738,8 +3759,11 @@
       <c r="H7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>260</v>
       </c>
@@ -3763,6 +3787,9 @@
       </c>
       <c r="H8">
         <v>7</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Base Day TUE.xlsx
+++ b/Data/Base Day TUE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="Denne_projektmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\UNI\MSc DTU\Masterarbeit\RollingStock\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44887652-818A-4CC8-8322-F4BCDDDAB171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFB6B02-701A-40D7-8700-3C3505CFF79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D5A09832-DCC1-4C14-988A-6790DFA22986}</author>
+  </authors>
+  <commentList>
+    <comment ref="A31" authorId="0" shapeId="0" xr:uid="{D5A09832-DCC1-4C14-988A-6790DFA22986}">
+      <text>
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
+    There was a spelling mistake: it was Talco with a c before</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="326">
   <si>
@@ -1033,7 +1051,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1064,6 +1082,12 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1214,6 +1238,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Lukas Egkher" id="{C017F3F1-EF36-4905-B0C6-E2CF00B0F431}" userId="36c6e3171e52559e" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1477,6 +1507,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A31" dT="2026-03-19T12:30:14.23" personId="{C017F3F1-EF36-4905-B0C6-E2CF00B0F431}" id="{D5A09832-DCC1-4C14-988A-6790DFA22986}">
+    <text>There was a spelling mistake: it was Talco with a c before</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Ark1">
@@ -3799,7 +3837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Ark9">
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
@@ -3964,7 +4002,7 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -3993,6 +4031,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Data/Base Day TUE.xlsx
+++ b/Data/Base Day TUE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="Denne_projektmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\UNI\MSc DTU\Masterarbeit\RollingStock\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44887652-818A-4CC8-8322-F4BCDDDAB171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32221BC0-66DC-42E9-A382-EFDCC0874E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual" sheetId="1" r:id="rId1"/>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">

--- a/Data/Base Day TUE.xlsx
+++ b/Data/Base Day TUE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="Denne_projektmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\UNI\MSc DTU\Masterarbeit\RollingStock\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFB6B02-701A-40D7-8700-3C3505CFF79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31947851-F5AB-4655-BEA2-3DF92E0444B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="325">
   <si>
     <t>Settings</t>
   </si>
@@ -706,9 +706,6 @@
   </si>
   <si>
     <t>IC3 togsæt med Indusi</t>
-  </si>
-  <si>
-    <t>EB15Talco</t>
   </si>
   <si>
     <t>Gennemgående tog uden kobling/afkobling</t>
@@ -1051,7 +1048,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1082,12 +1079,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1543,7 +1534,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1554,7 +1545,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1565,7 +1556,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1576,7 +1567,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,7 +1583,7 @@
       </c>
       <c r="C9" s="23"/>
       <c r="D9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,7 +1591,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,7 +1599,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1640,7 +1631,7 @@
       </c>
       <c r="C16" s="23"/>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,7 +1642,7 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,7 +1653,7 @@
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1673,7 +1664,7 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1684,7 +1675,7 @@
         <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,7 +1686,7 @@
         <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1711,7 +1702,7 @@
       </c>
       <c r="C24" s="23"/>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,10 +1739,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1787,11 +1778,11 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C35" s="23"/>
       <c r="D35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1799,10 +1790,10 @@
         <v>40</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D36" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,7 +1809,7 @@
       </c>
       <c r="C39" s="23"/>
       <c r="D39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1829,7 +1820,7 @@
         <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1837,10 +1828,10 @@
         <v>44</v>
       </c>
       <c r="C41" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D41" t="s">
         <v>294</v>
-      </c>
-      <c r="D41" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1851,7 +1842,7 @@
         <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1862,7 +1853,7 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1873,7 +1864,7 @@
         <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1884,7 +1875,7 @@
         <v>52</v>
       </c>
       <c r="D45" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1895,7 +1886,7 @@
         <v>54</v>
       </c>
       <c r="D46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1906,7 +1897,7 @@
         <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1917,7 +1908,7 @@
         <v>58</v>
       </c>
       <c r="D48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1928,7 +1919,7 @@
         <v>60</v>
       </c>
       <c r="D49" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1939,7 +1930,7 @@
         <v>62</v>
       </c>
       <c r="D50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1950,7 +1941,7 @@
         <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1961,7 +1952,7 @@
         <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1972,7 +1963,7 @@
         <v>68</v>
       </c>
       <c r="D53" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1983,7 +1974,7 @@
         <v>70</v>
       </c>
       <c r="D54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1994,7 +1985,7 @@
         <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2005,7 +1996,7 @@
         <v>74</v>
       </c>
       <c r="D56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2016,13 +2007,13 @@
         <v>76</v>
       </c>
       <c r="D57" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D58" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E58" s="5"/>
     </row>
@@ -2040,7 +2031,7 @@
       </c>
       <c r="C60" s="23"/>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E60" s="5"/>
     </row>
@@ -2052,7 +2043,7 @@
         <v>80</v>
       </c>
       <c r="D61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2063,7 +2054,7 @@
         <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2074,7 +2065,7 @@
         <v>84</v>
       </c>
       <c r="D63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2085,7 +2076,7 @@
         <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2101,7 +2092,7 @@
       </c>
       <c r="C67" s="23"/>
       <c r="D67" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2112,19 +2103,19 @@
         <v>89</v>
       </c>
       <c r="D68" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D69" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E69" s="3"/>
     </row>
@@ -2136,7 +2127,7 @@
         <v>91</v>
       </c>
       <c r="D70" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E70" s="3"/>
     </row>
@@ -2148,7 +2139,7 @@
         <v>93</v>
       </c>
       <c r="D71" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E71" s="3"/>
     </row>
@@ -2160,7 +2151,7 @@
         <v>95</v>
       </c>
       <c r="D72" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E72" s="3"/>
     </row>
@@ -2172,7 +2163,7 @@
         <v>97</v>
       </c>
       <c r="D73" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E73" s="3"/>
     </row>
@@ -2461,15 +2452,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>263</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2488,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2499,7 +2490,7 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2518,7 +2509,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3612,7 +3603,7 @@
         <v>37</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>99</v>
@@ -3624,7 +3615,7 @@
         <v>103</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -3803,10 +3794,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" t="s">
         <v>260</v>
-      </c>
-      <c r="B8" t="s">
-        <v>261</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3862,122 +3853,122 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -3997,12 +3988,12 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -4012,17 +4003,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
@@ -4172,10 +4163,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4231,10 +4222,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -4290,10 +4281,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="S4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -4349,10 +4340,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4394,7 +4385,7 @@
         <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4450,7 +4441,7 @@
         <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4506,7 +4497,7 @@
         <v>184</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -4559,7 +4550,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B14" t="s">
         <v>205</v>
@@ -4573,7 +4564,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B15" t="s">
         <v>203</v>
@@ -4587,7 +4578,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
         <v>212</v>
@@ -4601,7 +4592,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B17" t="s">
         <v>210</v>
@@ -4618,7 +4609,7 @@
         <v>183</v>
       </c>
       <c r="B18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -4671,10 +4662,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -4685,7 +4676,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s">
         <v>210</v>
@@ -4730,7 +4721,7 @@
         <v>179</v>
       </c>
       <c r="B26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -4741,7 +4732,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s">
         <v>203</v>
@@ -4769,10 +4760,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -4828,7 +4819,7 @@
         <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4909,7 +4900,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B39" t="s">
         <v>203</v>
@@ -4923,7 +4914,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B40" t="s">
         <v>105</v>
@@ -4937,7 +4928,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B41" t="s">
         <v>208</v>
@@ -4951,7 +4942,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B42" t="s">
         <v>203</v>
@@ -4968,7 +4959,7 @@
         <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4993,10 +4984,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -5010,7 +5001,7 @@
         <v>170</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -5035,7 +5026,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
         <v>205</v>
@@ -5049,7 +5040,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
         <v>203</v>
@@ -5063,7 +5054,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s">
         <v>212</v>
@@ -5080,7 +5071,7 @@
         <v>166</v>
       </c>
       <c r="B51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5105,7 +5096,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B53" t="s">
         <v>203</v>
@@ -5200,7 +5191,7 @@
         <v>79</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>90</v>
@@ -5340,7 +5331,7 @@
         <v>186</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -5480,7 +5471,7 @@
         <v>185</v>
       </c>
       <c r="B15" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C15">
         <v>10000</v>
@@ -5620,7 +5611,7 @@
         <v>187</v>
       </c>
       <c r="B22" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C22">
         <v>10000</v>
@@ -5760,7 +5751,7 @@
         <v>184</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C29">
         <v>10000</v>
@@ -5777,7 +5768,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B30" t="s">
         <v>203</v>
@@ -5797,7 +5788,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s">
         <v>205</v>
@@ -5817,7 +5808,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s">
         <v>210</v>
@@ -5837,7 +5828,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
         <v>105</v>
@@ -5857,7 +5848,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s">
         <v>208</v>
@@ -5877,7 +5868,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B35" t="s">
         <v>212</v>
@@ -5897,10 +5888,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C36">
         <v>10000</v>
@@ -6040,7 +6031,7 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C43">
         <v>10000</v>
@@ -6180,7 +6171,7 @@
         <v>182</v>
       </c>
       <c r="B50" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C50">
         <v>10000</v>
@@ -6320,7 +6311,7 @@
         <v>181</v>
       </c>
       <c r="B57" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C57">
         <v>10000</v>
@@ -6460,7 +6451,7 @@
         <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C64">
         <v>10000</v>
@@ -6600,7 +6591,7 @@
         <v>179</v>
       </c>
       <c r="B71" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C71">
         <v>10000</v>
@@ -6617,7 +6608,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B72" t="s">
         <v>203</v>
@@ -6637,7 +6628,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B73" t="s">
         <v>205</v>
@@ -6657,7 +6648,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B74" t="s">
         <v>210</v>
@@ -6677,7 +6668,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B75" t="s">
         <v>105</v>
@@ -6697,7 +6688,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B76" t="s">
         <v>208</v>
@@ -6717,7 +6708,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B77" t="s">
         <v>212</v>
@@ -6737,10 +6728,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B78" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C78">
         <v>10000</v>
@@ -6757,7 +6748,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s">
         <v>203</v>
@@ -6777,7 +6768,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
         <v>205</v>
@@ -6797,7 +6788,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" t="s">
         <v>210</v>
@@ -6817,7 +6808,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B82" t="s">
         <v>105</v>
@@ -6837,7 +6828,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s">
         <v>208</v>
@@ -6857,7 +6848,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B84" t="s">
         <v>212</v>
@@ -6877,10 +6868,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B85" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C85">
         <v>10000</v>
@@ -7020,7 +7011,7 @@
         <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C92">
         <v>10000</v>
@@ -7160,7 +7151,7 @@
         <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C99">
         <v>10000</v>
@@ -7300,7 +7291,7 @@
         <v>176</v>
       </c>
       <c r="B106" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C106">
         <v>10000</v>
@@ -7440,7 +7431,7 @@
         <v>175</v>
       </c>
       <c r="B113" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C113">
         <v>10000</v>
@@ -7457,7 +7448,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B114" t="s">
         <v>203</v>
@@ -7477,7 +7468,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B115" t="s">
         <v>205</v>
@@ -7497,7 +7488,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B116" t="s">
         <v>210</v>
@@ -7517,7 +7508,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B117" t="s">
         <v>105</v>
@@ -7537,7 +7528,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B118" t="s">
         <v>208</v>
@@ -7557,7 +7548,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B119" t="s">
         <v>212</v>
@@ -7577,10 +7568,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B120" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C120">
         <v>10000</v>
@@ -7597,7 +7588,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B121" t="s">
         <v>203</v>
@@ -7617,7 +7608,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B122" t="s">
         <v>205</v>
@@ -7637,7 +7628,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B123" t="s">
         <v>210</v>
@@ -7657,7 +7648,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B124" t="s">
         <v>105</v>
@@ -7677,7 +7668,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B125" t="s">
         <v>208</v>
@@ -7697,7 +7688,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B126" t="s">
         <v>212</v>
@@ -7717,10 +7708,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B127" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C127">
         <v>10000</v>
@@ -7860,7 +7851,7 @@
         <v>173</v>
       </c>
       <c r="B134" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C134">
         <v>10000</v>
@@ -8000,7 +7991,7 @@
         <v>172</v>
       </c>
       <c r="B141" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C141">
         <v>10000</v>
@@ -8140,7 +8131,7 @@
         <v>169</v>
       </c>
       <c r="B148" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C148">
         <v>10000</v>
@@ -8280,7 +8271,7 @@
         <v>167</v>
       </c>
       <c r="B155" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C155">
         <v>10000</v>
@@ -8297,7 +8288,7 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B156" t="s">
         <v>203</v>
@@ -8317,7 +8308,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B157" t="s">
         <v>205</v>
@@ -8337,7 +8328,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B158" t="s">
         <v>210</v>
@@ -8357,7 +8348,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B159" t="s">
         <v>105</v>
@@ -8377,7 +8368,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B160" t="s">
         <v>208</v>
@@ -8397,7 +8388,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B161" t="s">
         <v>212</v>
@@ -8417,10 +8408,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B162" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C162">
         <v>10000</v>
@@ -8560,7 +8551,7 @@
         <v>188</v>
       </c>
       <c r="B169" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C169">
         <v>10000</v>
@@ -8700,7 +8691,7 @@
         <v>192</v>
       </c>
       <c r="B176" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C176">
         <v>10000</v>

--- a/Data/Base Day TUE.xlsx
+++ b/Data/Base Day TUE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meine Ablage\UNI\MSc DTU\Masterarbeit\RollingStock\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31947851-F5AB-4655-BEA2-3DF92E0444B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487B0154-1385-4975-BEB1-3DFAA753174D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual" sheetId="1" r:id="rId1"/>
